--- a/artfynd/A 42969-2025 artfynd.xlsx
+++ b/artfynd/A 42969-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90739</v>
+        <v>90742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>127675667</v>
       </c>
       <c r="B15" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 42969-2025 artfynd.xlsx
+++ b/artfynd/A 42969-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90742</v>
+        <v>90834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42969-2025 artfynd.xlsx
+++ b/artfynd/A 42969-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90834</v>
+        <v>90846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42969-2025 artfynd.xlsx
+++ b/artfynd/A 42969-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90846</v>
+        <v>90848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42969-2025 artfynd.xlsx
+++ b/artfynd/A 42969-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90848</v>
+        <v>90849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42969-2025 artfynd.xlsx
+++ b/artfynd/A 42969-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90849</v>
+        <v>90876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42969-2025 artfynd.xlsx
+++ b/artfynd/A 42969-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90876</v>
+        <v>90886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42969-2025 artfynd.xlsx
+++ b/artfynd/A 42969-2025 artfynd.xlsx
@@ -1807,7 +1807,7 @@
         <v>125971359</v>
       </c>
       <c r="B12" t="n">
-        <v>90886</v>
+        <v>90890</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
